--- a/data/dividends.xlsx
+++ b/data/dividends.xlsx
@@ -436,16 +436,16 @@
         <v>3</v>
       </c>
       <c r="D2" t="str">
-        <v>Coal India Ltd</v>
+        <v>HCL Technologies Ltd</v>
       </c>
       <c r="E2">
-        <v>5000</v>
+        <v>48</v>
       </c>
       <c r="F2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>4500</v>
+        <v>48</v>
       </c>
       <c r="H2" t="str">
         <v>FY26 final dividend</v>
